--- a/Assignments/Jan-May-2026/investment_and_portfolio_management_coursera/course2_portfolio_selection_and_risk_management/assignment3/Assignment3_MeanVarianceFrontier_Part1.xlsx
+++ b/Assignments/Jan-May-2026/investment_and_portfolio_management_coursera/course2_portfolio_selection_and_risk_management/assignment3/Assignment3_MeanVarianceFrontier_Part1.xlsx
@@ -67,10 +67,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000%"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -233,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -310,6 +311,9 @@
     </xf>
     <xf borderId="7" fillId="4" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -711,10 +715,10 @@
         <v>0.0</v>
       </c>
       <c r="H6" s="26">
-        <v>0.1497</v>
+        <v>0.1589</v>
       </c>
       <c r="I6" s="26">
-        <v>0.2298</v>
+        <v>0.243</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -722,12 +726,12 @@
         <v>13</v>
       </c>
       <c r="M6" s="28">
-        <v>0.46</v>
-      </c>
-      <c r="N6" s="26">
+        <v>0.54</v>
+      </c>
+      <c r="N6" s="29">
         <v>0.153932</v>
       </c>
-      <c r="O6" s="26">
+      <c r="O6" s="29">
         <v>0.194494</v>
       </c>
       <c r="P6" s="2"/>
@@ -736,9 +740,9 @@
     </row>
     <row r="7" ht="20.25" customHeight="1">
       <c r="A7" s="18"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="25">
@@ -746,22 +750,22 @@
         <v>0.01</v>
       </c>
       <c r="H7" s="26">
-        <v>0.149792</v>
+        <v>0.158808</v>
       </c>
       <c r="I7" s="26">
-        <v>0.228383453099676</v>
+        <v>0.241402449137808</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="32">
         <f>1-M6</f>
-        <v>0.54</v>
-      </c>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
+        <v>0.46</v>
+      </c>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -782,10 +786,10 @@
         <v>0.02</v>
       </c>
       <c r="H8" s="26">
-        <v>0.149884</v>
+        <v>0.158716</v>
       </c>
       <c r="I8" s="26">
-        <v>0.226989726607457</v>
+        <v>0.239824222265659</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -802,10 +806,10 @@
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>1.0</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <v>0.3581</v>
       </c>
       <c r="E9" s="2"/>
@@ -815,10 +819,10 @@
         <v>0.03</v>
       </c>
       <c r="H9" s="26">
-        <v>0.149976</v>
+        <v>0.158624</v>
       </c>
       <c r="I9" s="26">
-        <v>0.225619243431911</v>
+        <v>0.238265703379207</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -835,10 +839,10 @@
       <c r="B10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <v>0.3581</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>1.0</v>
       </c>
       <c r="E10" s="2"/>
@@ -848,10 +852,10 @@
         <v>0.04</v>
       </c>
       <c r="H10" s="26">
-        <v>0.150068</v>
+        <v>0.158532</v>
       </c>
       <c r="I10" s="26">
-        <v>0.224272429678978</v>
+        <v>0.236727281727544</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -875,10 +879,10 @@
         <v>0.05</v>
       </c>
       <c r="H11" s="26">
-        <v>0.15016</v>
+        <v>0.15844</v>
       </c>
       <c r="I11" s="26">
-        <v>0.222949714301903</v>
+        <v>0.235209351657837</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -902,10 +906,10 @@
         <v>0.06</v>
       </c>
       <c r="H12" s="26">
-        <v>0.150252</v>
+        <v>0.158348</v>
       </c>
       <c r="I12" s="26">
-        <v>0.221651528725502</v>
+        <v>0.233712312440641</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -929,10 +933,10 @@
         <v>0.07</v>
       </c>
       <c r="H13" s="26">
-        <v>0.150344</v>
+        <v>0.158256</v>
       </c>
       <c r="I13" s="26">
-        <v>0.220378306444323</v>
+        <v>0.23223656807503</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -956,10 +960,10 @@
         <v>0.08</v>
       </c>
       <c r="H14" s="26">
-        <v>0.150436</v>
+        <v>0.158164</v>
       </c>
       <c r="I14" s="26">
-        <v>0.219130482594385</v>
+        <v>0.230782527072671</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -983,10 +987,10 @@
         <v>0.09</v>
       </c>
       <c r="H15" s="26">
-        <v>0.150528</v>
+        <v>0.158072</v>
       </c>
       <c r="I15" s="26">
-        <v>0.217908493498285</v>
+        <v>0.229350602220033</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1010,10 +1014,10 @@
         <v>0.1</v>
       </c>
       <c r="H16" s="26">
-        <v>0.15062</v>
+        <v>0.15798</v>
       </c>
       <c r="I16" s="26">
-        <v>0.216712776183593</v>
+        <v>0.227941210317924</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1037,10 +1041,10 @@
         <v>0.11</v>
       </c>
       <c r="H17" s="26">
-        <v>0.150712</v>
+        <v>0.157888</v>
       </c>
       <c r="I17" s="26">
-        <v>0.215543767874583</v>
+        <v>0.226554771897597</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1064,10 +1068,10 @@
         <v>0.12</v>
       </c>
       <c r="H18" s="26">
-        <v>0.150804</v>
+        <v>0.157796</v>
       </c>
       <c r="I18" s="26">
-        <v>0.214401905457503</v>
+        <v>0.225191710912742</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1091,10 +1095,10 @@
         <v>0.13</v>
       </c>
       <c r="H19" s="26">
-        <v>0.150896</v>
+        <v>0.157704</v>
       </c>
       <c r="I19" s="26">
-        <v>0.21328762491975</v>
+        <v>0.22385245440671</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1118,10 +1122,10 @@
         <v>0.14</v>
       </c>
       <c r="H20" s="26">
-        <v>0.150988</v>
+        <v>0.157612</v>
       </c>
       <c r="I20" s="26">
-        <v>0.212201360763479</v>
+        <v>0.222537432154395</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1145,10 +1149,10 @@
         <v>0.15</v>
       </c>
       <c r="H21" s="26">
-        <v>0.15108</v>
+        <v>0.15752</v>
       </c>
       <c r="I21" s="26">
-        <v>0.21114354539436</v>
+        <v>0.221247076278309</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1172,10 +1176,10 @@
         <v>0.16</v>
       </c>
       <c r="H22" s="26">
-        <v>0.151172</v>
+        <v>0.157428</v>
       </c>
       <c r="I22" s="26">
-        <v>0.210114608486397</v>
+        <v>0.219981820838432</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1199,10 +1203,10 @@
         <v>0.17</v>
       </c>
       <c r="H23" s="26">
-        <v>0.151264</v>
+        <v>0.157336</v>
       </c>
       <c r="I23" s="26">
-        <v>0.209114976323907</v>
+        <v>0.218742101395566</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -1226,10 +1230,10 @@
         <v>0.18</v>
       </c>
       <c r="H24" s="26">
-        <v>0.151356</v>
+        <v>0.157244</v>
       </c>
       <c r="I24" s="26">
-        <v>0.208145071121965</v>
+        <v>0.217528354548018</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1253,10 +1257,10 @@
         <v>0.19</v>
       </c>
       <c r="H25" s="26">
-        <v>0.151448</v>
+        <v>0.157152</v>
       </c>
       <c r="I25" s="26">
-        <v>0.207205310326864</v>
+        <v>0.216341017441566</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1280,10 +1284,10 @@
         <v>0.2</v>
       </c>
       <c r="H26" s="26">
-        <v>0.15154</v>
+        <v>0.15706</v>
       </c>
       <c r="I26" s="26">
-        <v>0.206296105898294</v>
+        <v>0.215180527252816</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1307,10 +1311,10 @@
         <v>0.21</v>
       </c>
       <c r="H27" s="26">
-        <v>0.151632</v>
+        <v>0.156968</v>
       </c>
       <c r="I27" s="26">
-        <v>0.205417863575231</v>
+        <v>0.214047320646188</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1334,10 +1338,10 @@
         <v>0.22</v>
       </c>
       <c r="H28" s="26">
-        <v>0.151724</v>
+        <v>0.156876</v>
       </c>
       <c r="I28" s="26">
-        <v>0.204570982127691</v>
+        <v>0.212941833204958</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1361,10 +1365,10 @@
         <v>0.23</v>
       </c>
       <c r="H29" s="26">
-        <v>0.151816</v>
+        <v>0.156784</v>
       </c>
       <c r="I29" s="26">
-        <v>0.203755852596749</v>
+        <v>0.211864498836941</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -1388,10 +1392,10 @@
         <v>0.24</v>
       </c>
       <c r="H30" s="26">
-        <v>0.151908</v>
+        <v>0.156692</v>
       </c>
       <c r="I30" s="26">
-        <v>0.202972857525414</v>
+        <v>0.210815749155589</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -1415,10 +1419,10 @@
         <v>0.25</v>
       </c>
       <c r="H31" s="26">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="I31" s="26">
-        <v>0.202222370183172</v>
+        <v>0.20979601283747</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1442,10 +1446,10 @@
         <v>0.26</v>
       </c>
       <c r="H32" s="26">
-        <v>0.152092</v>
+        <v>0.156508</v>
       </c>
       <c r="I32" s="26">
-        <v>0.20150475378718</v>
+        <v>0.208805714957307</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -1469,10 +1473,10 @@
         <v>0.27</v>
       </c>
       <c r="H33" s="26">
-        <v>0.152184</v>
+        <v>0.156416</v>
       </c>
       <c r="I33" s="26">
-        <v>0.200820360723279</v>
+        <v>0.207845276301936</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -1496,10 +1500,10 @@
         <v>0.28</v>
       </c>
       <c r="H34" s="26">
-        <v>0.152276</v>
+        <v>0.156324</v>
       </c>
       <c r="I34" s="26">
-        <v>0.200169531770167</v>
+        <v>0.206915112664803</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -1523,10 +1527,10 @@
         <v>0.29</v>
       </c>
       <c r="H35" s="26">
-        <v>0.152368</v>
+        <v>0.156232</v>
       </c>
       <c r="I35" s="26">
-        <v>0.199552595330184</v>
+        <v>0.206015634122782</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -1550,10 +1554,10 @@
         <v>0.3</v>
       </c>
       <c r="H36" s="26">
-        <v>0.15246</v>
+        <v>0.15614</v>
       </c>
       <c r="I36" s="26">
-        <v>0.198969866670308</v>
+        <v>0.205147244297358</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -1577,10 +1581,10 @@
         <v>0.31</v>
       </c>
       <c r="H37" s="26">
-        <v>0.152552</v>
+        <v>0.156048</v>
       </c>
       <c r="I37" s="26">
-        <v>0.198421647177046</v>
+        <v>0.20431033960241</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -1604,10 +1608,10 @@
         <v>0.32</v>
       </c>
       <c r="H38" s="26">
-        <v>0.152644</v>
+        <v>0.155956</v>
       </c>
       <c r="I38" s="26">
-        <v>0.197908223628954</v>
+        <v>0.203505308481052</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -1631,10 +1635,10 @@
         <v>0.33</v>
       </c>
       <c r="H39" s="26">
-        <v>0.152736</v>
+        <v>0.155864</v>
       </c>
       <c r="I39" s="26">
-        <v>0.19742986749058</v>
+        <v>0.202732530634203</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -1658,10 +1662,10 @@
         <v>0.34</v>
       </c>
       <c r="H40" s="26">
-        <v>0.152828</v>
+        <v>0.155772</v>
       </c>
       <c r="I40" s="26">
-        <v>0.196986834231611</v>
+        <v>0.201992376243738</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -1685,10 +1689,10 @@
         <v>0.35</v>
       </c>
       <c r="H41" s="26">
-        <v>0.15292</v>
+        <v>0.15568</v>
       </c>
       <c r="I41" s="26">
-        <v>0.196579362674977</v>
+        <v>0.201285205193278</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -1712,10 +1716,10 @@
         <v>0.36</v>
       </c>
       <c r="H42" s="26">
-        <v>0.153012</v>
+        <v>0.155588</v>
       </c>
       <c r="I42" s="26">
-        <v>0.196207674377615</v>
+        <v>0.200611366289829</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -1739,10 +1743,10 @@
         <v>0.37</v>
       </c>
       <c r="H43" s="26">
-        <v>0.153104</v>
+        <v>0.155496</v>
       </c>
       <c r="I43" s="26">
-        <v>0.195871973047468</v>
+        <v>0.199971196489665</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -1766,10 +1770,10 @@
         <v>0.38</v>
       </c>
       <c r="H44" s="26">
-        <v>0.153196</v>
+        <v>0.155404</v>
       </c>
       <c r="I44" s="26">
-        <v>0.195572444000191</v>
+        <v>0.199365020131938</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -1793,10 +1797,10 @@
         <v>0.39</v>
       </c>
       <c r="H45" s="26">
-        <v>0.153288</v>
+        <v>0.155312</v>
       </c>
       <c r="I45" s="26">
-        <v>0.195309253658837</v>
+        <v>0.198793148183664</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -1820,10 +1824,10 @@
         <v>0.4</v>
       </c>
       <c r="H46" s="26">
-        <v>0.15338</v>
+        <v>0.15522</v>
       </c>
       <c r="I46" s="26">
-        <v>0.195082549099606</v>
+        <v>0.19825587749976</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -1847,10 +1851,10 @@
         <v>0.41</v>
       </c>
       <c r="H47" s="26">
-        <v>0.153472</v>
+        <v>0.155128</v>
       </c>
       <c r="I47" s="26">
-        <v>0.194892457646498</v>
+        <v>0.197753490101925</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -1874,10 +1878,10 @@
         <v>0.42</v>
       </c>
       <c r="H48" s="26">
-        <v>0.153564</v>
+        <v>0.155036</v>
       </c>
       <c r="I48" s="26">
-        <v>0.194739086517443</v>
+        <v>0.197286252480116</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -1901,10 +1905,10 @@
         <v>0.43</v>
       </c>
       <c r="H49" s="26">
-        <v>0.153656</v>
+        <v>0.154944</v>
       </c>
       <c r="I49" s="26">
-        <v>0.194622522524162</v>
+        <v>0.196854414920438</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -1928,10 +1932,10 @@
         <v>0.44</v>
       </c>
       <c r="H50" s="26">
-        <v>0.153748</v>
+        <v>0.154852</v>
       </c>
       <c r="I50" s="26">
-        <v>0.194542831827729</v>
+        <v>0.196458210863155</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -1955,10 +1959,10 @@
         <v>0.45</v>
       </c>
       <c r="H51" s="26">
-        <v>0.15384</v>
+        <v>0.15476</v>
       </c>
       <c r="I51" s="26">
-        <v>0.194500059751405</v>
+        <v>0.196097856294504</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -1982,10 +1986,10 @@
         <v>0.46</v>
       </c>
       <c r="H52" s="26">
-        <v>0.153932</v>
+        <v>0.154668</v>
       </c>
       <c r="I52" s="26">
-        <v>0.194494230651997</v>
+        <v>0.195773549175858</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -2009,10 +2013,10 @@
         <v>0.47</v>
       </c>
       <c r="H53" s="26">
-        <v>0.154024</v>
+        <v>0.154576</v>
       </c>
       <c r="I53" s="26">
-        <v>0.194525347850577</v>
+        <v>0.195485468913646</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -2036,10 +2040,10 @@
         <v>0.48</v>
       </c>
       <c r="H54" s="26">
-        <v>0.154116</v>
+        <v>0.154484</v>
       </c>
       <c r="I54" s="26">
-        <v>0.194593393623031</v>
+        <v>0.195233775873254</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -2063,10 +2067,10 @@
         <v>0.49</v>
       </c>
       <c r="H55" s="26">
-        <v>0.154208</v>
+        <v>0.154392</v>
       </c>
       <c r="I55" s="26">
-        <v>0.194698329250489</v>
+        <v>0.19501861093991</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -2117,10 +2121,10 @@
         <v>0.51</v>
       </c>
       <c r="H57" s="26">
-        <v>0.154392</v>
+        <v>0.154208</v>
       </c>
       <c r="I57" s="26">
-        <v>0.19501861093991</v>
+        <v>0.194698329250489</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -2144,10 +2148,10 @@
         <v>0.52</v>
       </c>
       <c r="H58" s="26">
-        <v>0.154484</v>
+        <v>0.154116</v>
       </c>
       <c r="I58" s="26">
-        <v>0.195233775873254</v>
+        <v>0.194593393623031</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -2171,10 +2175,10 @@
         <v>0.53</v>
       </c>
       <c r="H59" s="26">
-        <v>0.154576</v>
+        <v>0.154024</v>
       </c>
       <c r="I59" s="26">
-        <v>0.195485468913646</v>
+        <v>0.194525347850577</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -2198,10 +2202,10 @@
         <v>0.54</v>
       </c>
       <c r="H60" s="26">
-        <v>0.154668</v>
+        <v>0.153932</v>
       </c>
       <c r="I60" s="26">
-        <v>0.195773549175858</v>
+        <v>0.194494230651997</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -2225,10 +2229,10 @@
         <v>0.55</v>
       </c>
       <c r="H61" s="26">
-        <v>0.15476</v>
+        <v>0.15384</v>
       </c>
       <c r="I61" s="26">
-        <v>0.196097856294504</v>
+        <v>0.194500059751405</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -2252,10 +2256,10 @@
         <v>0.56</v>
       </c>
       <c r="H62" s="26">
-        <v>0.154852</v>
+        <v>0.153748</v>
       </c>
       <c r="I62" s="26">
-        <v>0.196458210863155</v>
+        <v>0.194542831827729</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -2279,10 +2283,10 @@
         <v>0.57</v>
       </c>
       <c r="H63" s="26">
-        <v>0.154944</v>
+        <v>0.153656</v>
       </c>
       <c r="I63" s="26">
-        <v>0.196854414920438</v>
+        <v>0.194622522524162</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -2306,10 +2310,10 @@
         <v>0.58</v>
       </c>
       <c r="H64" s="26">
-        <v>0.155036</v>
+        <v>0.153564</v>
       </c>
       <c r="I64" s="26">
-        <v>0.197286252480116</v>
+        <v>0.194739086517443</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -2333,10 +2337,10 @@
         <v>0.59</v>
       </c>
       <c r="H65" s="26">
-        <v>0.155128</v>
+        <v>0.153472</v>
       </c>
       <c r="I65" s="26">
-        <v>0.197753490101925</v>
+        <v>0.194892457646498</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
@@ -2360,10 +2364,10 @@
         <v>0.6</v>
       </c>
       <c r="H66" s="26">
-        <v>0.15522</v>
+        <v>0.15338</v>
       </c>
       <c r="I66" s="26">
-        <v>0.19825587749976</v>
+        <v>0.195082549099606</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -2387,10 +2391,10 @@
         <v>0.61</v>
       </c>
       <c r="H67" s="26">
-        <v>0.155312</v>
+        <v>0.153288</v>
       </c>
       <c r="I67" s="26">
-        <v>0.198793148183664</v>
+        <v>0.195309253658837</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -2414,10 +2418,10 @@
         <v>0.62</v>
       </c>
       <c r="H68" s="26">
-        <v>0.155404</v>
+        <v>0.153196</v>
       </c>
       <c r="I68" s="26">
-        <v>0.199365020131938</v>
+        <v>0.195572444000191</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
@@ -2441,10 +2445,10 @@
         <v>0.63</v>
       </c>
       <c r="H69" s="26">
-        <v>0.155496</v>
+        <v>0.153104</v>
       </c>
       <c r="I69" s="26">
-        <v>0.199971196489665</v>
+        <v>0.195871973047468</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -2468,10 +2472,10 @@
         <v>0.64</v>
       </c>
       <c r="H70" s="26">
-        <v>0.155588</v>
+        <v>0.153012</v>
       </c>
       <c r="I70" s="26">
-        <v>0.200611366289829</v>
+        <v>0.196207674377615</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -2495,10 +2499,10 @@
         <v>0.65</v>
       </c>
       <c r="H71" s="26">
-        <v>0.15568</v>
+        <v>0.15292</v>
       </c>
       <c r="I71" s="26">
-        <v>0.201285205193278</v>
+        <v>0.196579362674977</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -2522,10 +2526,10 @@
         <v>0.66</v>
       </c>
       <c r="H72" s="26">
-        <v>0.155772</v>
+        <v>0.152828</v>
       </c>
       <c r="I72" s="26">
-        <v>0.201992376243739</v>
+        <v>0.196986834231611</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -2549,10 +2553,10 @@
         <v>0.67</v>
       </c>
       <c r="H73" s="26">
-        <v>0.155864</v>
+        <v>0.152736</v>
       </c>
       <c r="I73" s="26">
-        <v>0.202732530634203</v>
+        <v>0.19742986749058</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -2576,10 +2580,10 @@
         <v>0.68</v>
       </c>
       <c r="H74" s="26">
-        <v>0.155956</v>
+        <v>0.152644</v>
       </c>
       <c r="I74" s="26">
-        <v>0.203505308481052</v>
+        <v>0.197908223628954</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -2603,10 +2607,10 @@
         <v>0.69</v>
       </c>
       <c r="H75" s="26">
-        <v>0.156048</v>
+        <v>0.152552</v>
       </c>
       <c r="I75" s="26">
-        <v>0.20431033960241</v>
+        <v>0.198421647177046</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
@@ -2630,10 +2634,10 @@
         <v>0.7</v>
       </c>
       <c r="H76" s="26">
-        <v>0.15614</v>
+        <v>0.15246</v>
       </c>
       <c r="I76" s="26">
-        <v>0.205147244297358</v>
+        <v>0.198969866670308</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -2657,10 +2661,10 @@
         <v>0.71</v>
       </c>
       <c r="H77" s="26">
-        <v>0.156232</v>
+        <v>0.152368</v>
       </c>
       <c r="I77" s="26">
-        <v>0.206015634122782</v>
+        <v>0.199552595330184</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
@@ -2684,10 +2688,10 @@
         <v>0.72</v>
       </c>
       <c r="H78" s="26">
-        <v>0.156324</v>
+        <v>0.152276</v>
       </c>
       <c r="I78" s="26">
-        <v>0.206915112664803</v>
+        <v>0.200169531770167</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -2711,10 +2715,10 @@
         <v>0.73</v>
       </c>
       <c r="H79" s="26">
-        <v>0.156416</v>
+        <v>0.152184</v>
       </c>
       <c r="I79" s="26">
-        <v>0.207845276301936</v>
+        <v>0.200820360723279</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
@@ -2738,10 +2742,10 @@
         <v>0.74</v>
       </c>
       <c r="H80" s="26">
-        <v>0.156508</v>
+        <v>0.152092</v>
       </c>
       <c r="I80" s="26">
-        <v>0.208805714957307</v>
+        <v>0.20150475378718</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -2765,10 +2769,10 @@
         <v>0.75</v>
       </c>
       <c r="H81" s="26">
-        <v>0.1566</v>
+        <v>0.152</v>
       </c>
       <c r="I81" s="26">
-        <v>0.20979601283747</v>
+        <v>0.202222370183172</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
@@ -2792,10 +2796,10 @@
         <v>0.76</v>
       </c>
       <c r="H82" s="26">
-        <v>0.156692</v>
+        <v>0.151908</v>
       </c>
       <c r="I82" s="26">
-        <v>0.210815749155589</v>
+        <v>0.202972857525414</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
@@ -2819,10 +2823,10 @@
         <v>0.77</v>
       </c>
       <c r="H83" s="26">
-        <v>0.156784</v>
+        <v>0.151816</v>
       </c>
       <c r="I83" s="26">
-        <v>0.211864498836941</v>
+        <v>0.203755852596749</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -2846,10 +2850,10 @@
         <v>0.78</v>
       </c>
       <c r="H84" s="26">
-        <v>0.156876</v>
+        <v>0.151724</v>
       </c>
       <c r="I84" s="26">
-        <v>0.212941833204958</v>
+        <v>0.204570982127691</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
@@ -2873,10 +2877,10 @@
         <v>0.79</v>
       </c>
       <c r="H85" s="26">
-        <v>0.156968</v>
+        <v>0.151632</v>
       </c>
       <c r="I85" s="26">
-        <v>0.214047320646188</v>
+        <v>0.205417863575231</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
@@ -2900,10 +2904,10 @@
         <v>0.8</v>
       </c>
       <c r="H86" s="26">
-        <v>0.15706</v>
+        <v>0.15154</v>
       </c>
       <c r="I86" s="26">
-        <v>0.215180527252816</v>
+        <v>0.206296105898294</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
@@ -2927,10 +2931,10 @@
         <v>0.81</v>
       </c>
       <c r="H87" s="26">
-        <v>0.157152</v>
+        <v>0.151448</v>
       </c>
       <c r="I87" s="26">
-        <v>0.216341017441566</v>
+        <v>0.207205310326864</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -2954,10 +2958,10 @@
         <v>0.82</v>
       </c>
       <c r="H88" s="26">
-        <v>0.157244</v>
+        <v>0.151356</v>
       </c>
       <c r="I88" s="26">
-        <v>0.217528354548018</v>
+        <v>0.208145071121965</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
@@ -2981,10 +2985,10 @@
         <v>0.83</v>
       </c>
       <c r="H89" s="26">
-        <v>0.157336</v>
+        <v>0.151264</v>
       </c>
       <c r="I89" s="26">
-        <v>0.218742101395566</v>
+        <v>0.209114976323907</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
@@ -3008,10 +3012,10 @@
         <v>0.84</v>
       </c>
       <c r="H90" s="26">
-        <v>0.157428</v>
+        <v>0.151172</v>
       </c>
       <c r="I90" s="26">
-        <v>0.219981820838432</v>
+        <v>0.210114608486397</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
@@ -3035,10 +3039,10 @@
         <v>0.85</v>
       </c>
       <c r="H91" s="26">
-        <v>0.15752</v>
+        <v>0.15108</v>
       </c>
       <c r="I91" s="26">
-        <v>0.221247076278309</v>
+        <v>0.21114354539436</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
@@ -3062,10 +3066,10 @@
         <v>0.86</v>
       </c>
       <c r="H92" s="26">
-        <v>0.157612</v>
+        <v>0.150988</v>
       </c>
       <c r="I92" s="26">
-        <v>0.222537432154395</v>
+        <v>0.212201360763479</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
@@ -3089,10 +3093,10 @@
         <v>0.87</v>
       </c>
       <c r="H93" s="26">
-        <v>0.157704</v>
+        <v>0.150896</v>
       </c>
       <c r="I93" s="26">
-        <v>0.22385245440671</v>
+        <v>0.21328762491975</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -3116,10 +3120,10 @@
         <v>0.88</v>
       </c>
       <c r="H94" s="26">
-        <v>0.157796</v>
+        <v>0.150804</v>
       </c>
       <c r="I94" s="26">
-        <v>0.225191710912742</v>
+        <v>0.214401905457503</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
@@ -3143,10 +3147,10 @@
         <v>0.89</v>
       </c>
       <c r="H95" s="26">
-        <v>0.157888</v>
+        <v>0.150712</v>
       </c>
       <c r="I95" s="26">
-        <v>0.226554771897597</v>
+        <v>0.215543767874583</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
@@ -3170,10 +3174,10 @@
         <v>0.9</v>
       </c>
       <c r="H96" s="26">
-        <v>0.15798</v>
+        <v>0.15062</v>
       </c>
       <c r="I96" s="26">
-        <v>0.227941210317924</v>
+        <v>0.216712776183593</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -3197,10 +3201,10 @@
         <v>0.91</v>
       </c>
       <c r="H97" s="26">
-        <v>0.158072</v>
+        <v>0.150528</v>
       </c>
       <c r="I97" s="26">
-        <v>0.229350602220033</v>
+        <v>0.217908493498285</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
@@ -3224,10 +3228,10 @@
         <v>0.92</v>
       </c>
       <c r="H98" s="26">
-        <v>0.158164</v>
+        <v>0.150436</v>
       </c>
       <c r="I98" s="26">
-        <v>0.230782527072671</v>
+        <v>0.219130482594385</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
@@ -3251,10 +3255,10 @@
         <v>0.93</v>
       </c>
       <c r="H99" s="26">
-        <v>0.158256</v>
+        <v>0.150344</v>
       </c>
       <c r="I99" s="26">
-        <v>0.23223656807503</v>
+        <v>0.220378306444323</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
@@ -3278,10 +3282,10 @@
         <v>0.94</v>
       </c>
       <c r="H100" s="26">
-        <v>0.158348</v>
+        <v>0.150252</v>
       </c>
       <c r="I100" s="26">
-        <v>0.233712312440641</v>
+        <v>0.221651528725502</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
@@ -3305,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="H101" s="26">
-        <v>0.15844</v>
+        <v>0.15016</v>
       </c>
       <c r="I101" s="26">
-        <v>0.235209351657837</v>
+        <v>0.222949714301903</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
@@ -3332,10 +3336,10 @@
         <v>0.96</v>
       </c>
       <c r="H102" s="26">
-        <v>0.158532</v>
+        <v>0.150068</v>
       </c>
       <c r="I102" s="26">
-        <v>0.236727281727544</v>
+        <v>0.224272429678978</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
@@ -3359,10 +3363,10 @@
         <v>0.97</v>
       </c>
       <c r="H103" s="26">
-        <v>0.158624</v>
+        <v>0.149976</v>
       </c>
       <c r="I103" s="26">
-        <v>0.238265703379207</v>
+        <v>0.225619243431911</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
@@ -3386,10 +3390,10 @@
         <v>0.98</v>
       </c>
       <c r="H104" s="26">
-        <v>0.158716</v>
+        <v>0.149884</v>
       </c>
       <c r="I104" s="26">
-        <v>0.239824222265659</v>
+        <v>0.226989726607457</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -3413,10 +3417,10 @@
         <v>0.99</v>
       </c>
       <c r="H105" s="26">
-        <v>0.158808</v>
+        <v>0.149792</v>
       </c>
       <c r="I105" s="26">
-        <v>0.241402449137808</v>
+        <v>0.228383453099676</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
@@ -3440,10 +3444,10 @@
         <v>1</v>
       </c>
       <c r="H106" s="26">
-        <v>0.1589</v>
+        <v>0.1497</v>
       </c>
       <c r="I106" s="26">
-        <v>0.243</v>
+        <v>0.2298</v>
       </c>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
